--- a/Vivienda/4_carga/ced_vivienda_global.xlsx
+++ b/Vivienda/4_carga/ced_vivienda_global.xlsx
@@ -576,7 +576,7 @@
         <v>7.6</v>
       </c>
       <c r="M6">
-        <v>0.55</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         <v>10.6</v>
       </c>
       <c r="M7">
-        <v>0.49</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         <v>12.9</v>
       </c>
       <c r="M8">
-        <v>0.47</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="9">
@@ -706,7 +706,7 @@
         <v>13.8</v>
       </c>
       <c r="M9">
-        <v>0.44</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="10">
@@ -752,7 +752,7 @@
         <v>15.5</v>
       </c>
       <c r="M10">
-        <v>0.43</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +798,7 @@
         <v>13.4</v>
       </c>
       <c r="M11">
-        <v>0.41</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
         <v>15.8</v>
       </c>
       <c r="M12">
-        <v>0.4</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="13">
@@ -896,7 +896,7 @@
         <v>13.8</v>
       </c>
       <c r="M13">
-        <v>0.41</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="14">
@@ -945,7 +945,7 @@
         <v>13.2</v>
       </c>
       <c r="M14">
-        <v>0.43</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="15">
@@ -994,7 +994,7 @@
         <v>11.2</v>
       </c>
       <c r="M15">
-        <v>0.45</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="16">
@@ -1043,7 +1043,7 @@
         <v>15.7</v>
       </c>
       <c r="M16">
-        <v>0.5</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="17">
@@ -1092,7 +1092,7 @@
         <v>11.3</v>
       </c>
       <c r="M17">
-        <v>0.52</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="18">
@@ -1141,7 +1141,7 @@
         <v>19</v>
       </c>
       <c r="M18">
-        <v>0.55</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="19">
@@ -1205,7 +1205,7 @@
         <v>17</v>
       </c>
       <c r="M20">
-        <v>0.53</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="21">
@@ -1269,7 +1269,7 @@
         <v>16.3</v>
       </c>
       <c r="M22">
-        <v>0.55</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="23">
@@ -1333,7 +1333,7 @@
         <v>15.6</v>
       </c>
       <c r="M24">
-        <v>0.58</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="25">
@@ -1366,7 +1366,7 @@
         <v>15.24</v>
       </c>
       <c r="M25">
-        <v>0.62</v>
+        <v>49.96</v>
       </c>
     </row>
     <row r="26">
@@ -1430,7 +1430,7 @@
         <v>14.87</v>
       </c>
       <c r="M27">
-        <v>0.67</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="28">
@@ -1494,7 +1494,7 @@
         <v>14.67</v>
       </c>
       <c r="M29">
-        <v>0.7</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="30">
@@ -1659,7 +1659,7 @@
         <v>3.4</v>
       </c>
       <c r="M35">
-        <v>0.5</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="36">
@@ -1705,7 +1705,7 @@
         <v>3.4</v>
       </c>
       <c r="M36">
-        <v>0.45</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="37">
@@ -1743,7 +1743,7 @@
         <v>5.5</v>
       </c>
       <c r="M37">
-        <v>0.42</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="38">
@@ -1789,7 +1789,7 @@
         <v>5.5</v>
       </c>
       <c r="M38">
-        <v>0.42</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="39">
@@ -1835,7 +1835,7 @@
         <v>4.1</v>
       </c>
       <c r="M39">
-        <v>0.42</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="40">
@@ -1881,7 +1881,7 @@
         <v>11.6</v>
       </c>
       <c r="M40">
-        <v>0.39</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="41">
@@ -1930,7 +1930,7 @@
         <v>11.1</v>
       </c>
       <c r="M41">
-        <v>0.36</v>
+        <v>28.79</v>
       </c>
     </row>
     <row r="42">
@@ -1979,7 +1979,7 @@
         <v>8.1</v>
       </c>
       <c r="M42">
-        <v>0.37</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="43">
@@ -2028,7 +2028,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M43">
-        <v>0.39</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="44">
@@ -2077,7 +2077,7 @@
         <v>3.7</v>
       </c>
       <c r="M44">
-        <v>0.39</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="45">
@@ -2126,7 +2126,7 @@
         <v>3.9</v>
       </c>
       <c r="M45">
-        <v>0.4</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="46">
@@ -2175,7 +2175,7 @@
         <v>3.8</v>
       </c>
       <c r="M46">
-        <v>0.43</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="47">
@@ -2224,7 +2224,7 @@
         <v>5.4</v>
       </c>
       <c r="M47">
-        <v>0.44</v>
+        <v>35.08</v>
       </c>
     </row>
     <row r="48">
@@ -2288,7 +2288,7 @@
         <v>12.4</v>
       </c>
       <c r="M49">
-        <v>0.43</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="50">
@@ -2352,7 +2352,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M51">
-        <v>0.43</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="52">
@@ -2416,7 +2416,7 @@
         <v>11.9</v>
       </c>
       <c r="M53">
-        <v>0.43</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="54">
@@ -2449,7 +2449,7 @@
         <v>10.02</v>
       </c>
       <c r="M54">
-        <v>0.45</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="55">
@@ -2513,7 +2513,7 @@
         <v>11.24</v>
       </c>
       <c r="M56">
-        <v>0.49</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="57">
@@ -2577,7 +2577,7 @@
         <v>11.05</v>
       </c>
       <c r="M58">
-        <v>0.5</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="59">
@@ -2742,7 +2742,7 @@
         <v>11</v>
       </c>
       <c r="M64">
-        <v>0.68</v>
+        <v>54.03</v>
       </c>
     </row>
     <row r="65">
@@ -2780,7 +2780,7 @@
         <v>20.8</v>
       </c>
       <c r="M65">
-        <v>0.59</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="66">
@@ -2818,7 +2818,7 @@
         <v>15.1</v>
       </c>
       <c r="M66">
-        <v>0.57</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="67">
@@ -2864,7 +2864,7 @@
         <v>12</v>
       </c>
       <c r="M67">
-        <v>0.52</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="68">
@@ -2902,7 +2902,7 @@
         <v>10.2</v>
       </c>
       <c r="M68">
-        <v>0.49</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="69">
@@ -2940,7 +2940,7 @@
         <v>20</v>
       </c>
       <c r="M69">
-        <v>0.47</v>
+        <v>37.45</v>
       </c>
     </row>
     <row r="70">
@@ -2989,7 +2989,7 @@
         <v>16.8</v>
       </c>
       <c r="M70">
-        <v>0.47</v>
+        <v>37.51</v>
       </c>
     </row>
     <row r="71">
@@ -3038,7 +3038,7 @@
         <v>18.9</v>
       </c>
       <c r="M71">
-        <v>0.47</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="72">
@@ -3087,7 +3087,7 @@
         <v>16.7</v>
       </c>
       <c r="M72">
-        <v>0.51</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="73">
@@ -3136,7 +3136,7 @@
         <v>21.1</v>
       </c>
       <c r="M73">
-        <v>0.5600000000000001</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="74">
@@ -3185,7 +3185,7 @@
         <v>11.9</v>
       </c>
       <c r="M74">
-        <v>0.64</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="75">
@@ -3234,7 +3234,7 @@
         <v>9.9</v>
       </c>
       <c r="M75">
-        <v>0.68</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="76">
@@ -3283,7 +3283,7 @@
         <v>23</v>
       </c>
       <c r="M76">
-        <v>0.67</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="77">
@@ -3347,7 +3347,7 @@
         <v>26.2</v>
       </c>
       <c r="M78">
-        <v>0.65</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="79">
@@ -3411,7 +3411,7 @@
         <v>20</v>
       </c>
       <c r="M80">
-        <v>0.68</v>
+        <v>54.41</v>
       </c>
     </row>
     <row r="81">
@@ -3475,7 +3475,7 @@
         <v>21.3</v>
       </c>
       <c r="M82">
-        <v>0.75</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="83">
@@ -3508,7 +3508,7 @@
         <v>17.92</v>
       </c>
       <c r="M83">
-        <v>0.8</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="84">
@@ -3572,7 +3572,7 @@
         <v>18.8</v>
       </c>
       <c r="M85">
-        <v>0.83</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="86">
@@ -3636,7 +3636,7 @@
         <v>18.85</v>
       </c>
       <c r="M87">
-        <v>0.84</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="88">
@@ -3801,7 +3801,7 @@
         <v>3.6</v>
       </c>
       <c r="M93">
-        <v>0.79</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="94">
@@ -3847,7 +3847,7 @@
         <v>4.5</v>
       </c>
       <c r="M94">
-        <v>0.64</v>
+        <v>50.82</v>
       </c>
     </row>
     <row r="95">
@@ -3885,7 +3885,7 @@
         <v>3.4</v>
       </c>
       <c r="M95">
-        <v>0.5600000000000001</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="96">
@@ -3923,7 +3923,7 @@
         <v>9</v>
       </c>
       <c r="M96">
-        <v>0.5</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="97">
@@ -3961,7 +3961,7 @@
         <v>3.2</v>
       </c>
       <c r="M97">
-        <v>0.48</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="98">
@@ -4007,7 +4007,7 @@
         <v>7.8</v>
       </c>
       <c r="M98">
-        <v>0.42</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="99">
@@ -4056,7 +4056,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M99">
-        <v>0.39</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="100">
@@ -4105,7 +4105,7 @@
         <v>6.3</v>
       </c>
       <c r="M100">
-        <v>0.38</v>
+        <v>30.59</v>
       </c>
     </row>
     <row r="101">
@@ -4154,7 +4154,7 @@
         <v>5.9</v>
       </c>
       <c r="M101">
-        <v>0.42</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="102">
@@ -4203,7 +4203,7 @@
         <v>2.3</v>
       </c>
       <c r="M102">
-        <v>0.43</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="103">
@@ -4252,7 +4252,7 @@
         <v>7.1</v>
       </c>
       <c r="M103">
-        <v>0.45</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="104">
@@ -4301,7 +4301,7 @@
         <v>3.1</v>
       </c>
       <c r="M104">
-        <v>0.44</v>
+        <v>35.03</v>
       </c>
     </row>
     <row r="105">
@@ -4350,7 +4350,7 @@
         <v>6.8</v>
       </c>
       <c r="M105">
-        <v>0.46</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="106">
@@ -4414,7 +4414,7 @@
         <v>9</v>
       </c>
       <c r="M107">
-        <v>0.47</v>
+        <v>37.39</v>
       </c>
     </row>
     <row r="108">
@@ -4478,7 +4478,7 @@
         <v>5.3</v>
       </c>
       <c r="M109">
-        <v>0.49</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="110">
@@ -4542,7 +4542,7 @@
         <v>7.2</v>
       </c>
       <c r="M111">
-        <v>0.51</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="112">
@@ -4575,7 +4575,7 @@
         <v>8.08</v>
       </c>
       <c r="M112">
-        <v>0.55</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="113">
@@ -4639,7 +4639,7 @@
         <v>7.73</v>
       </c>
       <c r="M114">
-        <v>0.57</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="115">
@@ -4703,7 +4703,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="M116">
-        <v>0.5600000000000001</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="117">
@@ -4876,7 +4876,7 @@
         <v>4</v>
       </c>
       <c r="M122">
-        <v>0.4</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="123">
@@ -4922,7 +4922,7 @@
         <v>7.2</v>
       </c>
       <c r="M123">
-        <v>0.36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124">
@@ -4968,7 +4968,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M124">
-        <v>0.36</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="125">
@@ -5014,7 +5014,7 @@
         <v>7.7</v>
       </c>
       <c r="M125">
-        <v>0.37</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="126">
@@ -5060,7 +5060,7 @@
         <v>6.6</v>
       </c>
       <c r="M126">
-        <v>0.39</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="127">
@@ -5106,7 +5106,7 @@
         <v>3.2</v>
       </c>
       <c r="M127">
-        <v>0.36</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="128">
@@ -5155,7 +5155,7 @@
         <v>4.7</v>
       </c>
       <c r="M128">
-        <v>0.35</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="129">
@@ -5204,7 +5204,7 @@
         <v>5.3</v>
       </c>
       <c r="M129">
-        <v>0.34</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="130">
@@ -5253,7 +5253,7 @@
         <v>5.8</v>
       </c>
       <c r="M130">
-        <v>0.35</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="131">
@@ -5302,7 +5302,7 @@
         <v>2.4</v>
       </c>
       <c r="M131">
-        <v>0.37</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="132">
@@ -5351,7 +5351,7 @@
         <v>3.2</v>
       </c>
       <c r="M132">
-        <v>0.38</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="133">
@@ -5400,7 +5400,7 @@
         <v>3.1</v>
       </c>
       <c r="M133">
-        <v>0.4</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="134">
@@ -5449,7 +5449,7 @@
         <v>6.9</v>
       </c>
       <c r="M134">
-        <v>0.41</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="135">
@@ -5513,7 +5513,7 @@
         <v>10</v>
       </c>
       <c r="M136">
-        <v>0.41</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="137">
@@ -5577,7 +5577,7 @@
         <v>10.4</v>
       </c>
       <c r="M138">
-        <v>0.41</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="139">
@@ -5641,7 +5641,7 @@
         <v>9.6</v>
       </c>
       <c r="M140">
-        <v>0.41</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="141">
@@ -5674,7 +5674,7 @@
         <v>9.539999999999999</v>
       </c>
       <c r="M141">
-        <v>0.44</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="142">
@@ -5738,7 +5738,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="M143">
-        <v>0.46</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="144">
@@ -5802,7 +5802,7 @@
         <v>10.39</v>
       </c>
       <c r="M145">
-        <v>0.48</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="146">
@@ -5975,7 +5975,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M151">
-        <v>0.4</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="152">
@@ -6021,7 +6021,7 @@
         <v>12.4</v>
       </c>
       <c r="M152">
-        <v>0.37</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="153">
@@ -6067,7 +6067,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M153">
-        <v>0.35</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="154">
@@ -6113,7 +6113,7 @@
         <v>9</v>
       </c>
       <c r="M154">
-        <v>0.35</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="155">
@@ -6159,7 +6159,7 @@
         <v>8.5</v>
       </c>
       <c r="M155">
-        <v>0.35</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="156">
@@ -6205,7 +6205,7 @@
         <v>15.5</v>
       </c>
       <c r="M156">
-        <v>0.32</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="157">
@@ -6254,7 +6254,7 @@
         <v>13.5</v>
       </c>
       <c r="M157">
-        <v>0.3</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="158">
@@ -6303,7 +6303,7 @@
         <v>13.1</v>
       </c>
       <c r="M158">
-        <v>0.3</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="159">
@@ -6352,7 +6352,7 @@
         <v>16.6</v>
       </c>
       <c r="M159">
-        <v>0.31</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="160">
@@ -6401,7 +6401,7 @@
         <v>4.9</v>
       </c>
       <c r="M160">
-        <v>0.32</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="161">
@@ -6450,7 +6450,7 @@
         <v>9.1</v>
       </c>
       <c r="M161">
-        <v>0.33</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="162">
@@ -6499,7 +6499,7 @@
         <v>6.2</v>
       </c>
       <c r="M162">
-        <v>0.34</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="163">
@@ -6548,7 +6548,7 @@
         <v>8.4</v>
       </c>
       <c r="M163">
-        <v>0.35</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="164">
@@ -6612,7 +6612,7 @@
         <v>14.2</v>
       </c>
       <c r="M165">
-        <v>0.36</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="166">
@@ -6676,7 +6676,7 @@
         <v>14.5</v>
       </c>
       <c r="M167">
-        <v>0.36</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="168">
@@ -6740,7 +6740,7 @@
         <v>13.1</v>
       </c>
       <c r="M169">
-        <v>0.37</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="170">
@@ -6773,7 +6773,7 @@
         <v>13.69</v>
       </c>
       <c r="M170">
-        <v>0.39</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="171">
@@ -6837,7 +6837,7 @@
         <v>13.36</v>
       </c>
       <c r="M172">
-        <v>0.42</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="173">
@@ -6901,7 +6901,7 @@
         <v>13.53</v>
       </c>
       <c r="M174">
-        <v>0.44</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="175">
@@ -7090,7 +7090,7 @@
         <v>8.6</v>
       </c>
       <c r="M180">
-        <v>0.64</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="181">
@@ -7136,7 +7136,7 @@
         <v>9</v>
       </c>
       <c r="M181">
-        <v>0.57</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="182">
@@ -7182,7 +7182,7 @@
         <v>12.1</v>
       </c>
       <c r="M182">
-        <v>0.5600000000000001</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="183">
@@ -7228,7 +7228,7 @@
         <v>6.5</v>
       </c>
       <c r="M183">
-        <v>0.55</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="184">
@@ -7274,7 +7274,7 @@
         <v>13</v>
       </c>
       <c r="M184">
-        <v>0.54</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="185">
@@ -7320,7 +7320,7 @@
         <v>10.6</v>
       </c>
       <c r="M185">
-        <v>0.51</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="186">
@@ -7369,7 +7369,7 @@
         <v>10.5</v>
       </c>
       <c r="M186">
-        <v>0.51</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="187">
@@ -7418,7 +7418,7 @@
         <v>11.9</v>
       </c>
       <c r="M187">
-        <v>0.55</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="188">
@@ -7467,7 +7467,7 @@
         <v>9.9</v>
       </c>
       <c r="M188">
-        <v>0.61</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="189">
@@ -7516,7 +7516,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M189">
-        <v>0.6899999999999999</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="190">
@@ -7565,7 +7565,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M190">
-        <v>0.72</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="191">
@@ -7614,7 +7614,7 @@
         <v>8.1</v>
       </c>
       <c r="M191">
-        <v>0.73</v>
+        <v>58.37</v>
       </c>
     </row>
     <row r="192">
@@ -7663,7 +7663,7 @@
         <v>14.3</v>
       </c>
       <c r="M192">
-        <v>0.72</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="193">
@@ -7727,7 +7727,7 @@
         <v>14.2</v>
       </c>
       <c r="M194">
-        <v>0.65</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="195">
@@ -7791,7 +7791,7 @@
         <v>14.8</v>
       </c>
       <c r="M196">
-        <v>0.66</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="197">
@@ -7855,7 +7855,7 @@
         <v>14</v>
       </c>
       <c r="M198">
-        <v>0.71</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="199">
@@ -7888,7 +7888,7 @@
         <v>14.12</v>
       </c>
       <c r="M199">
-        <v>0.78</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="200">
@@ -7952,7 +7952,7 @@
         <v>14.03</v>
       </c>
       <c r="M201">
-        <v>0.83</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="202">
@@ -8016,7 +8016,7 @@
         <v>14</v>
       </c>
       <c r="M203">
-        <v>0.77</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="204">
@@ -8235,7 +8235,7 @@
         <v>9.9</v>
       </c>
       <c r="M211">
-        <v>0.37</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="212">
@@ -8281,7 +8281,7 @@
         <v>7.6</v>
       </c>
       <c r="M212">
-        <v>0.38</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="213">
@@ -8327,7 +8327,7 @@
         <v>5.5</v>
       </c>
       <c r="M213">
-        <v>0.41</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="214">
@@ -8373,7 +8373,7 @@
         <v>3.3</v>
       </c>
       <c r="M214">
-        <v>0.37</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="215">
@@ -8414,7 +8414,7 @@
         <v>6.3</v>
       </c>
       <c r="M215">
-        <v>0.34</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="216">
@@ -8455,7 +8455,7 @@
         <v>5.9</v>
       </c>
       <c r="M216">
-        <v>0.34</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="217">
@@ -8504,7 +8504,7 @@
         <v>5.5</v>
       </c>
       <c r="M217">
-        <v>0.35</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="218">
@@ -8553,7 +8553,7 @@
         <v>2.2</v>
       </c>
       <c r="M218">
-        <v>0.35</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="219">
@@ -8602,7 +8602,7 @@
         <v>10.3</v>
       </c>
       <c r="M219">
-        <v>0.38</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="220">
@@ -8651,7 +8651,7 @@
         <v>6.9</v>
       </c>
       <c r="M220">
-        <v>0.39</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="221">
@@ -8700,7 +8700,7 @@
         <v>11.4</v>
       </c>
       <c r="M221">
-        <v>0.4</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="222">
@@ -8764,7 +8764,7 @@
         <v>10.3</v>
       </c>
       <c r="M223">
-        <v>0.42</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="224">
@@ -8828,7 +8828,7 @@
         <v>10.8</v>
       </c>
       <c r="M225">
-        <v>0.42</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="226">
@@ -8892,7 +8892,7 @@
         <v>11.9</v>
       </c>
       <c r="M227">
-        <v>0.41</v>
+        <v>32.78</v>
       </c>
     </row>
     <row r="228">
@@ -8925,7 +8925,7 @@
         <v>11.83</v>
       </c>
       <c r="M228">
-        <v>0.44</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="229">
@@ -8989,7 +8989,7 @@
         <v>12.22</v>
       </c>
       <c r="M230">
-        <v>0.45</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="231">
@@ -9053,7 +9053,7 @@
         <v>12.17</v>
       </c>
       <c r="M232">
-        <v>0.44</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="233">
@@ -9234,7 +9234,7 @@
         <v>13.4</v>
       </c>
       <c r="M238">
-        <v>0.52</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="239">
@@ -9280,7 +9280,7 @@
         <v>18.7</v>
       </c>
       <c r="M239">
-        <v>0.45</v>
+        <v>36.02</v>
       </c>
     </row>
     <row r="240">
@@ -9326,7 +9326,7 @@
         <v>16.3</v>
       </c>
       <c r="M240">
-        <v>0.42</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="241">
@@ -9372,7 +9372,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M241">
-        <v>0.38</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="242">
@@ -9418,7 +9418,7 @@
         <v>15</v>
       </c>
       <c r="M242">
-        <v>0.37</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="243">
@@ -9464,7 +9464,7 @@
         <v>15.5</v>
       </c>
       <c r="M243">
-        <v>0.36</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="244">
@@ -9513,7 +9513,7 @@
         <v>19.5</v>
       </c>
       <c r="M244">
-        <v>0.35</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="245">
@@ -9562,7 +9562,7 @@
         <v>15.1</v>
       </c>
       <c r="M245">
-        <v>0.35</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="246">
@@ -9611,7 +9611,7 @@
         <v>12.8</v>
       </c>
       <c r="M246">
-        <v>0.38</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="247">
@@ -9660,7 +9660,7 @@
         <v>14.6</v>
       </c>
       <c r="M247">
-        <v>0.4</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="248">
@@ -9709,7 +9709,7 @@
         <v>7.6</v>
       </c>
       <c r="M248">
-        <v>0.43</v>
+        <v>34.11</v>
       </c>
     </row>
     <row r="249">
@@ -9758,7 +9758,7 @@
         <v>9.4</v>
       </c>
       <c r="M249">
-        <v>0.46</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="250">
@@ -9807,7 +9807,7 @@
         <v>14.4</v>
       </c>
       <c r="M250">
-        <v>0.48</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="251">
@@ -9871,7 +9871,7 @@
         <v>13.5</v>
       </c>
       <c r="M252">
-        <v>0.46</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="253">
@@ -9935,7 +9935,7 @@
         <v>12.2</v>
       </c>
       <c r="M254">
-        <v>0.48</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="255">
@@ -9999,7 +9999,7 @@
         <v>12.5</v>
       </c>
       <c r="M256">
-        <v>0.53</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="257">
@@ -10032,7 +10032,7 @@
         <v>13.99</v>
       </c>
       <c r="M257">
-        <v>0.59</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="258">
@@ -10096,7 +10096,7 @@
         <v>12.05</v>
       </c>
       <c r="M259">
-        <v>0.63</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="260">
@@ -10160,7 +10160,7 @@
         <v>12.74</v>
       </c>
       <c r="M261">
-        <v>0.65</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="262">
@@ -10341,7 +10341,7 @@
         <v>10.6</v>
       </c>
       <c r="M267">
-        <v>0.66</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="268">
@@ -10387,7 +10387,7 @@
         <v>12.3</v>
       </c>
       <c r="M268">
-        <v>0.64</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="269">
@@ -10433,7 +10433,7 @@
         <v>12.6</v>
       </c>
       <c r="M269">
-        <v>0.62</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="270">
@@ -10479,7 +10479,7 @@
         <v>6.6</v>
       </c>
       <c r="M270">
-        <v>0.63</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="271">
@@ -10525,7 +10525,7 @@
         <v>7.6</v>
       </c>
       <c r="M271">
-        <v>0.59</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="272">
@@ -10571,7 +10571,7 @@
         <v>11.1</v>
       </c>
       <c r="M272">
-        <v>0.5600000000000001</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="273">
@@ -10620,7 +10620,7 @@
         <v>10.3</v>
       </c>
       <c r="M273">
-        <v>0.55</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="274">
@@ -10669,7 +10669,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M274">
-        <v>0.59</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="275">
@@ -10718,7 +10718,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M275">
-        <v>0.63</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="276">
@@ -10767,7 +10767,7 @@
         <v>6.9</v>
       </c>
       <c r="M276">
-        <v>0.68</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="277">
@@ -10816,7 +10816,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M277">
-        <v>0.76</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="278">
@@ -10865,7 +10865,7 @@
         <v>7.2</v>
       </c>
       <c r="M278">
-        <v>0.76</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="279">
@@ -10914,7 +10914,7 @@
         <v>11.5</v>
       </c>
       <c r="M279">
-        <v>0.75</v>
+        <v>59.63</v>
       </c>
     </row>
     <row r="280">
@@ -10978,7 +10978,7 @@
         <v>13.2</v>
       </c>
       <c r="M281">
-        <v>0.67</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="282">
@@ -11042,7 +11042,7 @@
         <v>11.9</v>
       </c>
       <c r="M283">
-        <v>0.67</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="284">
@@ -11106,7 +11106,7 @@
         <v>13.8</v>
       </c>
       <c r="M285">
-        <v>0.71</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="286">
@@ -11139,7 +11139,7 @@
         <v>13</v>
       </c>
       <c r="M286">
-        <v>0.8100000000000001</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -11203,7 +11203,7 @@
         <v>13.7</v>
       </c>
       <c r="M288">
-        <v>0.88</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="289">
@@ -11267,7 +11267,7 @@
         <v>12.54</v>
       </c>
       <c r="M290">
-        <v>0.92</v>
+        <v>73.36</v>
       </c>
     </row>
     <row r="291">
@@ -11451,7 +11451,7 @@
         <v>1.8</v>
       </c>
       <c r="M297">
-        <v>0.39</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="298">
@@ -11497,7 +11497,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M298">
-        <v>0.37</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="299">
@@ -11535,7 +11535,7 @@
         <v>5.2</v>
       </c>
       <c r="M299">
-        <v>0.35</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="300">
@@ -11581,7 +11581,7 @@
         <v>7.3</v>
       </c>
       <c r="M300">
-        <v>0.35</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="301">
@@ -11619,7 +11619,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M301">
-        <v>0.33</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="302">
@@ -11668,7 +11668,7 @@
         <v>7.8</v>
       </c>
       <c r="M302">
-        <v>0.32</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="303">
@@ -11717,7 +11717,7 @@
         <v>6.3</v>
       </c>
       <c r="M303">
-        <v>0.31</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="304">
@@ -11766,7 +11766,7 @@
         <v>6.1</v>
       </c>
       <c r="M304">
-        <v>0.32</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="305">
@@ -11815,7 +11815,7 @@
         <v>11.3</v>
       </c>
       <c r="M305">
-        <v>0.32</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="306">
@@ -11864,7 +11864,7 @@
         <v>9.9</v>
       </c>
       <c r="M306">
-        <v>0.33</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="307">
@@ -11913,7 +11913,7 @@
         <v>10.1</v>
       </c>
       <c r="M307">
-        <v>0.35</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="308">
@@ -11962,7 +11962,7 @@
         <v>13.7</v>
       </c>
       <c r="M308">
-        <v>0.35</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="309">
@@ -12026,7 +12026,7 @@
         <v>11.8</v>
       </c>
       <c r="M310">
-        <v>0.36</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="311">
@@ -12090,7 +12090,7 @@
         <v>12.4</v>
       </c>
       <c r="M312">
-        <v>0.36</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="313">
@@ -12154,7 +12154,7 @@
         <v>13.4</v>
       </c>
       <c r="M314">
-        <v>0.37</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="315">
@@ -12187,7 +12187,7 @@
         <v>12.33</v>
       </c>
       <c r="M315">
-        <v>0.39</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="316">
@@ -12251,7 +12251,7 @@
         <v>13.01</v>
       </c>
       <c r="M317">
-        <v>0.39</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="318">
@@ -12315,7 +12315,7 @@
         <v>12.42</v>
       </c>
       <c r="M319">
-        <v>0.4</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="320">
@@ -12496,7 +12496,7 @@
         <v>3.4</v>
       </c>
       <c r="M325">
-        <v>0.62</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="326">
@@ -12534,7 +12534,7 @@
         <v>6.7</v>
       </c>
       <c r="M326">
-        <v>0.55</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="327">
@@ -12572,7 +12572,7 @@
         <v>7</v>
       </c>
       <c r="M327">
-        <v>0.47</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="328">
@@ -12618,7 +12618,7 @@
         <v>5.6</v>
       </c>
       <c r="M328">
-        <v>0.45</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="329">
@@ -12664,7 +12664,7 @@
         <v>7.6</v>
       </c>
       <c r="M329">
-        <v>0.45</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="330">
@@ -12702,7 +12702,7 @@
         <v>5.9</v>
       </c>
       <c r="M330">
-        <v>0.4</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="331">
@@ -12751,7 +12751,7 @@
         <v>7.4</v>
       </c>
       <c r="M331">
-        <v>0.39</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="332">
@@ -12800,7 +12800,7 @@
         <v>7.8</v>
       </c>
       <c r="M332">
-        <v>0.37</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="333">
@@ -12849,7 +12849,7 @@
         <v>6.4</v>
       </c>
       <c r="M333">
-        <v>0.36</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="334">
@@ -12898,7 +12898,7 @@
         <v>4.5</v>
       </c>
       <c r="M334">
-        <v>0.36</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="335">
@@ -12947,7 +12947,7 @@
         <v>3.9</v>
       </c>
       <c r="M335">
-        <v>0.38</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="336">
@@ -12996,7 +12996,7 @@
         <v>5.6</v>
       </c>
       <c r="M336">
-        <v>0.41</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="337">
@@ -13045,7 +13045,7 @@
         <v>8.5</v>
       </c>
       <c r="M337">
-        <v>0.42</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="338">
@@ -13109,7 +13109,7 @@
         <v>9</v>
       </c>
       <c r="M339">
-        <v>0.43</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="340">
@@ -13173,7 +13173,7 @@
         <v>9.4</v>
       </c>
       <c r="M341">
-        <v>0.43</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="342">
@@ -13237,7 +13237,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M343">
-        <v>0.44</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="344">
@@ -13270,7 +13270,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="M344">
-        <v>0.47</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="345">
@@ -13334,7 +13334,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M346">
-        <v>0.48</v>
+        <v>38.79</v>
       </c>
     </row>
     <row r="347">
@@ -13398,7 +13398,7 @@
         <v>10.11</v>
       </c>
       <c r="M348">
-        <v>0.48</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="349">
@@ -13563,7 +13563,7 @@
         <v>8.5</v>
       </c>
       <c r="M354">
-        <v>0.9</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="355">
@@ -13601,7 +13601,7 @@
         <v>18.6</v>
       </c>
       <c r="M355">
-        <v>0.74</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="356">
@@ -13639,7 +13639,7 @@
         <v>13.7</v>
       </c>
       <c r="M356">
-        <v>0.64</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="357">
@@ -13677,7 +13677,7 @@
         <v>17.4</v>
       </c>
       <c r="M357">
-        <v>0.57</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="358">
@@ -13715,7 +13715,7 @@
         <v>17.7</v>
       </c>
       <c r="M358">
-        <v>0.54</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="359">
@@ -13753,7 +13753,7 @@
         <v>19.4</v>
       </c>
       <c r="M359">
-        <v>0.51</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="360">
@@ -13794,7 +13794,7 @@
         <v>21.3</v>
       </c>
       <c r="M360">
-        <v>0.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="361">
@@ -13835,7 +13835,7 @@
         <v>21.7</v>
       </c>
       <c r="M361">
-        <v>0.54</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="362">
@@ -13884,7 +13884,7 @@
         <v>12.6</v>
       </c>
       <c r="M362">
-        <v>0.63</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="363">
@@ -13933,7 +13933,7 @@
         <v>15.4</v>
       </c>
       <c r="M363">
-        <v>0.75</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="364">
@@ -13982,7 +13982,7 @@
         <v>10.2</v>
       </c>
       <c r="M364">
-        <v>0.74</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="365">
@@ -14031,7 +14031,7 @@
         <v>14</v>
       </c>
       <c r="M365">
-        <v>0.74</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="366">
@@ -14080,7 +14080,7 @@
         <v>13.1</v>
       </c>
       <c r="M366">
-        <v>0.73</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="367">
@@ -14144,7 +14144,7 @@
         <v>20.3</v>
       </c>
       <c r="M368">
-        <v>0.66</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="369">
@@ -14208,7 +14208,7 @@
         <v>20.5</v>
       </c>
       <c r="M370">
-        <v>0.67</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="371">
@@ -14272,7 +14272,7 @@
         <v>15.8</v>
       </c>
       <c r="M372">
-        <v>0.8</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="373">
@@ -14305,7 +14305,7 @@
         <v>15.96</v>
       </c>
       <c r="M373">
-        <v>0.87</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="374">
@@ -14369,7 +14369,7 @@
         <v>15.69</v>
       </c>
       <c r="M375">
-        <v>0.91</v>
+        <v>72.94</v>
       </c>
     </row>
     <row r="376">
@@ -14433,7 +14433,7 @@
         <v>15.65</v>
       </c>
       <c r="M377">
-        <v>0.91</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="378">
@@ -14644,7 +14644,7 @@
         <v>12.3</v>
       </c>
       <c r="M385">
-        <v>0.41</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="386">
@@ -14690,7 +14690,7 @@
         <v>10.7</v>
       </c>
       <c r="M386">
-        <v>0.39</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="387">
@@ -14728,7 +14728,7 @@
         <v>10.8</v>
       </c>
       <c r="M387">
-        <v>0.4</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="388">
@@ -14774,7 +14774,7 @@
         <v>11</v>
       </c>
       <c r="M388">
-        <v>0.37</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="389">
@@ -14823,7 +14823,7 @@
         <v>11.4</v>
       </c>
       <c r="M389">
-        <v>0.32</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="390">
@@ -14872,7 +14872,7 @@
         <v>16.2</v>
       </c>
       <c r="M390">
-        <v>0.32</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="391">
@@ -14921,7 +14921,7 @@
         <v>12.5</v>
       </c>
       <c r="M391">
-        <v>0.32</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="392">
@@ -14970,7 +14970,7 @@
         <v>4.4</v>
       </c>
       <c r="M392">
-        <v>0.33</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="393">
@@ -15019,7 +15019,7 @@
         <v>7.9</v>
       </c>
       <c r="M393">
-        <v>0.35</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="394">
@@ -15068,7 +15068,7 @@
         <v>4.9</v>
       </c>
       <c r="M394">
-        <v>0.37</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="395">
@@ -15117,7 +15117,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M395">
-        <v>0.39</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="396">
@@ -15181,7 +15181,7 @@
         <v>8</v>
       </c>
       <c r="M397">
-        <v>0.39</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="398">
@@ -15245,7 +15245,7 @@
         <v>7.8</v>
       </c>
       <c r="M399">
-        <v>0.39</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="400">
@@ -15309,7 +15309,7 @@
         <v>10.4</v>
       </c>
       <c r="M401">
-        <v>0.39</v>
+        <v>31.09</v>
       </c>
     </row>
     <row r="402">
@@ -15342,7 +15342,7 @@
         <v>11.34</v>
       </c>
       <c r="M402">
-        <v>0.4</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="403">
@@ -15406,7 +15406,7 @@
         <v>13.01</v>
       </c>
       <c r="M404">
-        <v>0.43</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="405">
@@ -15470,7 +15470,7 @@
         <v>12.88</v>
       </c>
       <c r="M406">
-        <v>0.43</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="407">
@@ -15681,7 +15681,7 @@
         <v>4.9</v>
       </c>
       <c r="M414">
-        <v>0.52</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="415">
@@ -15727,7 +15727,7 @@
         <v>5.2</v>
       </c>
       <c r="M415">
-        <v>0.55</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="416">
@@ -15773,7 +15773,7 @@
         <v>3.9</v>
       </c>
       <c r="M416">
-        <v>0.54</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="417">
@@ -15819,7 +15819,7 @@
         <v>5.5</v>
       </c>
       <c r="M417">
-        <v>0.5</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="418">
@@ -15868,7 +15868,7 @@
         <v>5.7</v>
       </c>
       <c r="M418">
-        <v>0.46</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="419">
@@ -15917,7 +15917,7 @@
         <v>6.1</v>
       </c>
       <c r="M419">
-        <v>0.47</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="420">
@@ -15966,7 +15966,7 @@
         <v>6.5</v>
       </c>
       <c r="M420">
-        <v>0.48</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="421">
@@ -16015,7 +16015,7 @@
         <v>5.9</v>
       </c>
       <c r="M421">
-        <v>0.49</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="422">
@@ -16064,7 +16064,7 @@
         <v>5.4</v>
       </c>
       <c r="M422">
-        <v>0.52</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="423">
@@ -16113,7 +16113,7 @@
         <v>8.5</v>
       </c>
       <c r="M423">
-        <v>0.52</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="424">
@@ -16162,7 +16162,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M424">
-        <v>0.54</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="425">
@@ -16226,7 +16226,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M426">
-        <v>0.52</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="427">
@@ -16290,7 +16290,7 @@
         <v>7.2</v>
       </c>
       <c r="M428">
-        <v>0.51</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="429">
@@ -16354,7 +16354,7 @@
         <v>10.4</v>
       </c>
       <c r="M430">
-        <v>0.51</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="431">
@@ -16387,7 +16387,7 @@
         <v>9.57</v>
       </c>
       <c r="M431">
-        <v>0.55</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="432">
@@ -16451,7 +16451,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="M433">
-        <v>0.58</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="434">
@@ -16515,7 +16515,7 @@
         <v>9.73</v>
       </c>
       <c r="M435">
-        <v>0.6</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="436">
@@ -16672,7 +16672,7 @@
         <v>3.5</v>
       </c>
       <c r="M441">
-        <v>0.63</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="442">
@@ -16710,7 +16710,7 @@
         <v>5.3</v>
       </c>
       <c r="M442">
-        <v>0.51</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="443">
@@ -16748,7 +16748,7 @@
         <v>3.3</v>
       </c>
       <c r="M443">
-        <v>0.48</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="444">
@@ -16794,7 +16794,7 @@
         <v>2.6</v>
       </c>
       <c r="M444">
-        <v>0.45</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="445">
@@ -16840,7 +16840,7 @@
         <v>5.1</v>
       </c>
       <c r="M445">
-        <v>0.43</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="446">
@@ -16886,7 +16886,7 @@
         <v>7.5</v>
       </c>
       <c r="M446">
-        <v>0.39</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="447">
@@ -16935,7 +16935,7 @@
         <v>8.4</v>
       </c>
       <c r="M447">
-        <v>0.38</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="448">
@@ -16984,7 +16984,7 @@
         <v>6.5</v>
       </c>
       <c r="M448">
-        <v>0.36</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="449">
@@ -17033,7 +17033,7 @@
         <v>5.3</v>
       </c>
       <c r="M449">
-        <v>0.37</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="450">
@@ -17082,7 +17082,7 @@
         <v>5.8</v>
       </c>
       <c r="M450">
-        <v>0.38</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="451">
@@ -17131,7 +17131,7 @@
         <v>4.5</v>
       </c>
       <c r="M451">
-        <v>0.39</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="452">
@@ -17180,7 +17180,7 @@
         <v>4.8</v>
       </c>
       <c r="M452">
-        <v>0.39</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="453">
@@ -17229,7 +17229,7 @@
         <v>11.7</v>
       </c>
       <c r="M453">
-        <v>0.41</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="454">
@@ -17293,7 +17293,7 @@
         <v>10</v>
       </c>
       <c r="M455">
-        <v>0.41</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="456">
@@ -17357,7 +17357,7 @@
         <v>7.6</v>
       </c>
       <c r="M457">
-        <v>0.4</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="458">
@@ -17421,7 +17421,7 @@
         <v>9</v>
       </c>
       <c r="M459">
-        <v>0.41</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="460">
@@ -17454,7 +17454,7 @@
         <v>8.35</v>
       </c>
       <c r="M460">
-        <v>0.44</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="461">
@@ -17518,7 +17518,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="M462">
-        <v>0.47</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="463">
@@ -17582,7 +17582,7 @@
         <v>8.93</v>
       </c>
       <c r="M464">
-        <v>0.48</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="465">
@@ -17755,7 +17755,7 @@
         <v>8.5</v>
       </c>
       <c r="M470">
-        <v>0.49</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="471">
@@ -17801,7 +17801,7 @@
         <v>18.1</v>
       </c>
       <c r="M471">
-        <v>0.42</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="472">
@@ -17847,7 +17847,7 @@
         <v>20.4</v>
       </c>
       <c r="M472">
-        <v>0.39</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="473">
@@ -17885,7 +17885,7 @@
         <v>11.1</v>
       </c>
       <c r="M473">
-        <v>0.38</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="474">
@@ -17931,7 +17931,7 @@
         <v>14.1</v>
       </c>
       <c r="M474">
-        <v>0.38</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="475">
@@ -17977,7 +17977,7 @@
         <v>24.5</v>
       </c>
       <c r="M475">
-        <v>0.36</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="476">
@@ -18026,7 +18026,7 @@
         <v>19.5</v>
       </c>
       <c r="M476">
-        <v>0.34</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="477">
@@ -18075,7 +18075,7 @@
         <v>17.1</v>
       </c>
       <c r="M477">
-        <v>0.33</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="478">
@@ -18124,7 +18124,7 @@
         <v>14.9</v>
       </c>
       <c r="M478">
-        <v>0.35</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="479">
@@ -18173,7 +18173,7 @@
         <v>16.9</v>
       </c>
       <c r="M479">
-        <v>0.35</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="480">
@@ -18222,7 +18222,7 @@
         <v>14.9</v>
       </c>
       <c r="M480">
-        <v>0.37</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="481">
@@ -18271,7 +18271,7 @@
         <v>11.6</v>
       </c>
       <c r="M481">
-        <v>0.39</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="482">
@@ -18320,7 +18320,7 @@
         <v>15.5</v>
       </c>
       <c r="M482">
-        <v>0.4</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="483">
@@ -18384,7 +18384,7 @@
         <v>21.3</v>
       </c>
       <c r="M484">
-        <v>0.41</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="485">
@@ -18448,7 +18448,7 @@
         <v>12.3</v>
       </c>
       <c r="M486">
-        <v>0.43</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="487">
@@ -18512,7 +18512,7 @@
         <v>16.6</v>
       </c>
       <c r="M488">
-        <v>0.43</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="489">
@@ -18545,7 +18545,7 @@
         <v>17.25</v>
       </c>
       <c r="M489">
-        <v>0.45</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="490">
@@ -18609,7 +18609,7 @@
         <v>14.78</v>
       </c>
       <c r="M491">
-        <v>0.47</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="492">
@@ -18673,7 +18673,7 @@
         <v>15.39</v>
       </c>
       <c r="M493">
-        <v>0.47</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="494">
